--- a/sheets/조재수대금교본/검수/저녁 노을.xlsx
+++ b/sheets/조재수대금교본/검수/저녁 노을.xlsx
@@ -3690,17 +3690,9 @@
         </is>
       </c>
       <c r="O4" s="23"/>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
-      <c r="R4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="R4" s="21"/>
       <c r="S4" s="23"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
@@ -3718,17 +3710,12 @@
         </is>
       </c>
       <c r="C5" s="24"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -3795,11 +3782,7 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
@@ -3830,11 +3813,7 @@
     </row>
     <row r="7" ht="106.4" customHeight="true">
       <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B7" s="21"/>
       <c r="C7" s="23"/>
       <c r="D7" s="21"/>
       <c r="E7" s="23"/>
@@ -3842,11 +3821,7 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21"/>
       <c r="I7" s="23"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J7" s="21"/>
       <c r="K7" s="23"/>
       <c r="L7" s="21"/>
       <c r="M7" s="23"/>
@@ -3872,68 +3847,40 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶐
-‹</t>
+          <t xml:space="preserve">㶐</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R8" s="21"/>
       <c r="S8" s="24"/>
-      <c r="T8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T8" s="21"/>
       <c r="U8" s="24"/>
     </row>
     <row r="9" ht="106.4" customHeight="true">
@@ -3941,7 +3888,6 @@
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-ﾉ
 㴌</t>
         </is>
       </c>
@@ -4034,11 +3980,7 @@
         </is>
       </c>
       <c r="O10" s="23"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
@@ -4068,8 +4010,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋㳞
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -4091,22 +4032,16 @@
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-ﾉ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O11" s="24"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P11" s="21"/>
       <c r="Q11" s="24"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="S11" s="24"/>
@@ -4156,8 +4091,8 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢ㄴ
-–ﾉ</t>
+          <t xml:space="preserve">汰潢
+–</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -4215,29 +4150,13 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
@@ -4250,11 +4169,7 @@
       <c r="Q14" s="24"/>
       <c r="R14" s="21"/>
       <c r="S14" s="24"/>
-      <c r="T14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T14" s="21"/>
       <c r="U14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/저녁 노을.xlsx
+++ b/sheets/조재수대금교본/검수/저녁 노을.xlsx
@@ -3690,9 +3690,17 @@
         </is>
       </c>
       <c r="O4" s="23"/>
-      <c r="P4" s="21"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q4" s="23"/>
-      <c r="R4" s="21"/>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="S4" s="23"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
@@ -3782,7 +3790,11 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
@@ -3888,6 +3900,7 @@
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
+ﾉ
 㴌</t>
         </is>
       </c>
@@ -3980,7 +3993,11 @@
         </is>
       </c>
       <c r="O10" s="23"/>
-      <c r="P10" s="21"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
@@ -4010,7 +4027,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋㳞
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -4032,7 +4049,8 @@
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+ﾉ</t>
         </is>
       </c>
       <c r="O11" s="24"/>
@@ -4091,8 +4109,8 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
-–</t>
+          <t xml:space="preserve">汰潢ㄴ
+–ﾉ</t>
         </is>
       </c>
       <c r="Q12" s="22"/>

--- a/sheets/조재수대금교본/검수/저녁 노을.xlsx
+++ b/sheets/조재수대금교본/검수/저녁 노을.xlsx
@@ -3550,32 +3550,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="15.29" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="106.4" customHeight="true">
+    <row r="3" ht="152.99" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="106.4" customHeight="true">
+    <row r="4" ht="152.99" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="106.4" customHeight="true">
+    <row r="5" ht="152.99" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="106.4" customHeight="true">
+    <row r="6" ht="152.99" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="106.4" customHeight="true">
+    <row r="7" ht="152.99" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -3854,7 +3854,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="106.4" customHeight="true">
+    <row r="8" ht="152.99" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="106.4" customHeight="true">
+    <row r="9" ht="152.99" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="106.4" customHeight="true">
+    <row r="10" ht="152.99" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="106.4" customHeight="true">
+    <row r="11" ht="152.99" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="106.4" customHeight="true">
+    <row r="12" ht="152.99" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="106.4" customHeight="true">
+    <row r="13" ht="152.99" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4158,7 +4158,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="106.4" customHeight="true">
+    <row r="14" ht="152.99" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4196,6 +4196,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
 </worksheet>
 </file>